--- a/AAII_Financials/Quarterly/SLF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>SLF</t>
   </si>
@@ -656,316 +656,322 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6405900</v>
+      </c>
+      <c r="E8" s="3">
         <v>6275700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6376500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6409700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6207400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6082000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5804000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6348900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5855400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6026800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5911600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5888700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5643400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5620100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5738700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4790900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5159600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4666700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7751600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6991100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6584900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6352300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7814900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7309900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6719700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6499400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7722600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6547800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5963500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5572000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6225700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4358700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5138500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4511500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6435900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4134100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6044500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5384500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1817600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>6062900</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3726500</v>
+      </c>
+      <c r="E9" s="3">
         <v>3830600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3758200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3742600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3794400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3590600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3433300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3704800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3513700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3569800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3674800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3443400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3442800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3419800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2679400</v>
+      </c>
+      <c r="E10" s="3">
         <v>2445100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2618300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2667100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2413000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2491400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2370700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2644100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2341700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2456900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2236800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2445400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2200600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2200300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,56 +1467,59 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>64200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>138300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>-118900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-73400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-75400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>125100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1555,8 +1574,8 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>5</v>
+      <c r="AK14" s="3">
+        <v>0</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>5</v>
@@ -1573,53 +1592,56 @@
       <c r="AP14" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E15" s="3">
         <v>30800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>246500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>28000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>71100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>27100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>286300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>27800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>88600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>292300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>25900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>19600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>76700</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5394000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5742700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5416700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5310500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5428700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5157400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5084000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5035700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5124800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5184900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5250500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4924800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4970500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4810800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4904700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4623300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4181900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3983300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8616300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5307400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8217900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>73600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8232700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6866800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>11286900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4486600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5861600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7283200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7381400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8084600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5576500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3534600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4363200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3910000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6241700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3305000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5519100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4607800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>965700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>5141800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1011900</v>
+      </c>
+      <c r="E18" s="3">
         <v>533000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>959800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1099200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>778700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>924600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>720000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1313200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>730600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>841900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>661000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>964000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>672900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>809300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>834000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>167600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>977700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>683400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-864700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1683700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1633000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6278700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-417800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>443100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4567200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2012900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1861100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-735400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1417900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2512700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>649200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>824100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>775400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>601500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>194200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>829000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>525400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>776700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>852000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>921100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,101 +2056,102 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>14600</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>-34100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>94700</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-50600</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>93500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>86700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>74600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>71200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1869400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-687400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2577600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5215500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1198500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>381000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5197300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1420200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1075900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1424300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2082500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3197800</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
@@ -2146,53 +2179,56 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1042900</v>
+      </c>
+      <c r="E21" s="3">
         <v>563800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1191700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1127200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>849800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>951800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1040400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1339100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>758400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>930500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>858700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>989800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>743100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>886000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2268,374 +2304,386 @@
       <c r="AP21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>92200</v>
+      </c>
+      <c r="E22" s="3">
         <v>116800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>97000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>94000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>94600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>92500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>126500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>136900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>100800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>117400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>87100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>118300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>107200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>99800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>93500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>86700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>74600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>71200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>60700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>60000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>60800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>60100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>68900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>65900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>70600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>70700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>74800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>53900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>66600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>67700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>60100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>53000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>58700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>56500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>60300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>40900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>64700</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>61500</v>
       </c>
       <c r="AO22" s="3">
         <v>61500</v>
       </c>
       <c r="AP22" s="3">
+        <v>61500</v>
+      </c>
+      <c r="AQ22" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>919700</v>
+      </c>
+      <c r="E23" s="3">
         <v>416200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>784000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1005100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>684100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>832100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>489300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1176200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>629800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>843400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>552800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>845700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>616200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>784900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>834000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>167600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>977700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>683400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>944000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>936300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>883800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1003100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>711900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>758200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>559500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>522100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>710300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>635100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>597900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>617400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>589100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>771000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>716700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>545000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>134000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>788100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>460700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>715200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>790500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>862700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E24" s="3">
         <v>73800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>230500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>186700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>145200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>168400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>258500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>159100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>140300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>192700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-65900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>180400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>95900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>130800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-47800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>56100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>232800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>159200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>32600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>124400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>130200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>244000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>40200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>78200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>47900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>219000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>74800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>71400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>67700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>85200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>133700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>137000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>89600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-43900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>155500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-17100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>139800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>154400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>158300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>719700</v>
+      </c>
+      <c r="E26" s="3">
         <v>342400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>553600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>818400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>538900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>663700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>230700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1017100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>489500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>650600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>618600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>665300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>520300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>654100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>881900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>111500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>744900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>524200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>911400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>811900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>753600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>759100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>671600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>680000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>511700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>303000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>635400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>626800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>526600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>549700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>503800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>637300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>579600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>455400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>177900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>632600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>477800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>575400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>636100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>704500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>709800</v>
+      </c>
+      <c r="E27" s="3">
         <v>333100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>526600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>794000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>525000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>645600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>164700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>997800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>472000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>604100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>567200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>643900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>498400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>595700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>857600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>80900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>687300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>483500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>805500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>754800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>650900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>703600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>576400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>575000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>407300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>307000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>562100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>564600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>471800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>479600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>441400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>412000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>531500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>503600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>148800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>608000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>427200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>423300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>559300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>566200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3167,47 +3227,47 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>67700</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
         <v>-7400</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-800</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>5200</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,101 +3554,104 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>-14600</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>34100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>-94700</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>50600</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-93500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-86700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-74600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-71200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1869400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>687400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2577600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5215500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1198500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-381000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5197300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1420200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1075900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1424300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2082500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3197800</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
@@ -3610,130 +3679,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>725300</v>
+      </c>
+      <c r="E33" s="3">
         <v>347500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>541200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>808400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>538900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>659500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>178600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1012600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>486600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>618900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>582300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>657900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>513500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>610500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>925300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>80900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>687300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>483500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>798100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>754800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>650900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>703600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>575700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>575000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>407300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>307000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>560600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>564600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>471800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>479600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>441400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>412000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>531500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>503600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>154100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>608000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>427200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>423300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>559300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>566200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>725300</v>
+      </c>
+      <c r="E35" s="3">
         <v>347500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>541200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>808400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>538900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>659500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>178600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1012600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>486600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>618900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>582300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>657900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>513500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>610500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>925300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>80900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>687300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>483500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>798100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>754800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>650900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>703600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>575700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>575000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>407300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>307000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>560600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>564600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>471800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>479600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>441400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>412000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>531500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>503600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>154100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>608000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>427200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>423300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>559300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>566200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6263600</v>
+      </c>
+      <c r="E41" s="3">
         <v>6300100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7063600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6284100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5573900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5494800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7039700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7690100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6379300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5944800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8458100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6605800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6437100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6674700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6903200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6847400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5611900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4913100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5794100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6169600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6381000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6294500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8243500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7212500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7648900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5057300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5235500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5160800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5019000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4177000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5554400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4411000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4235200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4173500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4536700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4168300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4160100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3698300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>6639000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>6139700</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>76736100</v>
+      </c>
+      <c r="E42" s="3">
         <v>71813800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>65742600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>69124600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>66738500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>63535000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>57089000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>63420600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>58666600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>58822000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>53513100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>52494500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>56076100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>57814100</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,53 +4524,56 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E43" s="3">
         <v>164100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3061000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>201700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>209000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>198300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2158000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>304200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>148300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>132900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1967200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>153800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>161600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>175900</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4548,17 +4640,20 @@
       <c r="AM43" s="3">
         <v>0</v>
       </c>
-      <c r="AN43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO43" s="3">
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP43" s="3">
         <v>2152600</v>
       </c>
-      <c r="AP43" s="3" t="s">
+      <c r="AQ43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5667200</v>
+      </c>
+      <c r="E45" s="3">
         <v>5520600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6301400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5663800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6013800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5750200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6296700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5701200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5405300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5353300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6574900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5650700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6174300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5813000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>88886000</v>
+      </c>
+      <c r="E46" s="3">
         <v>83798500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>82847600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>81274200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>78535200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>74978300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>73512700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>77116100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>70599500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>70253000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>71373500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>64904800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>68849100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>70477700</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,374 +5024,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15377100</v>
+      </c>
+      <c r="E47" s="3">
         <v>14863200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>21265100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15510900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>15748000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>15237800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20195400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14994600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>15089300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14663400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>19989700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14039500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13985800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13888300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>110886900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>112000200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>110365200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>114269300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>122902700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>117415400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>113278700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>113944500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>121929100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>120529600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>122762400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>119078000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>113870800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>121190500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>111944300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>108093500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>103629300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>95237800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>100356700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>99454100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>97862100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>94758000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>96311200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>98931100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>96419000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>98671500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>1053200</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>973700</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>1098700</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>7436200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7396200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7228100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6856400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6743900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6369600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5904400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5732800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5815500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5677700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5810200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5777200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5696300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6081100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5732700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5388000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5447100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5283000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5523200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5452500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5259300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>5234800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>5196100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>5066500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>5064200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>4987300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10481700</v>
+      </c>
+      <c r="E49" s="3">
         <v>10597100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10813800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10697900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10482000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10418500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10196400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10495600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10424100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10510100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10824400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10421700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10337600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10265300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9885200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10001500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9835200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7117400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7319900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7330400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6991400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7278100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6614800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6646000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6347800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6459400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6171100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6536200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5600300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5475000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5473000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5073000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5305700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5245400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5097800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5018200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5123100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5357600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5393000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>5357600</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>140251400</v>
+      </c>
+      <c r="E52" s="3">
         <v>131342700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>128505900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>130199100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>125881000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>115241200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>110011500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>119461100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>112057100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>112671700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>104768200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>101675100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>106310200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>109393100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2551400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1573400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1532700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1398800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1368200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1228900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1134000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1175800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1264300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1138500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1203800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1260800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1134400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1186400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1034900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>983800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>920200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>815300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1002700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1011700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>963800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1096200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1117100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1064800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1112400</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1192300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>299507100</v>
+      </c>
+      <c r="E54" s="3">
         <v>285352400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>290605500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>283532100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>275898600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>259477500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>257652700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>267405900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>251719600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>251474800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>252334900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>232005900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>241610800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>245988600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>238211100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>234756200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>233136600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>240044900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>255698100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>245372300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>237894500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>238332700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>249929800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>239872500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>242039700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>228598700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>231719500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>242921600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>226810900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>217365600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>206884800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>196741900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>205813500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>203042500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>200275800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>194234300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>196338200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>200584100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>198386200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>199514700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1642100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1679300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3055200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1521300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1520000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1271100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3046900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1251000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1081400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1134300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3116700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1140600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1217300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1281600</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,85 +6239,88 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E58" s="3">
         <v>60200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3546000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>73300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3688400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>134700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>104900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3954900</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>113300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>133000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>80500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>98500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>68100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3">
         <v>134400</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -6222,17 +6355,20 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
-      <c r="AN58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO58" s="3">
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP58" s="3">
         <v>145200</v>
       </c>
-      <c r="AP58" s="3" t="s">
+      <c r="AQ58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6275,131 +6411,134 @@
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>393544300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>189328200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>190924000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>200751500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>215574300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>207836800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>201660500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>202033900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>212690700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>202449700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>202967500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>189350900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>195910000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>204607100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>192352600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>183708300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>173641900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>166350200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>174071400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>171658700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>169128400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>163182200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>164999500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>168698700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>170079200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>166743600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1659000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1739400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10356500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1521300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1593300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1291300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10143600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1385700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1081400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1239200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10428400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1140600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1330600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1414600</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,252 +6614,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10914700</v>
+      </c>
+      <c r="E61" s="3">
         <v>9999600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>13236600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9537700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9681300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7954200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10746900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9039600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9704500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7328700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10425300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4714100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5194800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5082700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5061500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5301700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4897300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4817200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4904900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3432600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3567600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3703200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4086200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3476700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3950400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3170800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3148300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3762200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3244200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3340200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3301600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3152400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3264900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3264100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4533000</v>
-      </c>
-      <c r="AL61" s="3">
-        <v>3227600</v>
       </c>
       <c r="AM61" s="3">
         <v>3227600</v>
       </c>
       <c r="AN61" s="3">
+        <v>3227600</v>
+      </c>
+      <c r="AO61" s="3">
         <v>3331000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>7968800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3944100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>267879700</v>
+      </c>
+      <c r="E62" s="3">
         <v>254806400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>247957100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>253599400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>245951200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>231916400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>218159800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>237577300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>222683700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>224501500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>212675000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>208356300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>217175700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>221810600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>344500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>545100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>526900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>233400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>238400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>280000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>299400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>289800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>296300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>312000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>306800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>245700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>316500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>329100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>311700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>252500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>245100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>260900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>353800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>322200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>299900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>555900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>571600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>569300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>527800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>487100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>280663300</v>
+      </c>
+      <c r="E66" s="3">
         <v>266762400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>272013400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>264873800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>257433300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>241361500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>239492900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>248213500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>233671900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>233274700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>234010300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>214436500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>224096800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>228686400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>221430000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>213825500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>212609600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>219978000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>234957700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>224973100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>218189000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>219042400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>229938400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>220045600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>222118300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>208782500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>212626100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>222876800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>208029000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>199057700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>188184800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>180148600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>188336800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>185875900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>183664300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>177640000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>179730400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>183510200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>181518900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>182917900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,112 +7659,115 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1576600</v>
+      </c>
+      <c r="E70" s="3">
         <v>1604000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1633000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1607400</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1641700</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>1557700</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>1556100</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>1657400</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>1635900</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>1653500</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>1695400</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>1655100</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1690800</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1654800</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1648200</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>1631700</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>1654600</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1627800</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1657700</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>1874800</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>2346100</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1694700</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>1746400</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>1730300</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>1771200</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>1771900</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>1759700</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>1871200</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>1789800</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>1737500</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>1717800</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>1640100</v>
-      </c>
-      <c r="AI70" s="3">
-        <v>1699000</v>
       </c>
       <c r="AJ70" s="3">
         <v>1699000</v>
       </c>
       <c r="AK70" s="3">
-        <v>1679700</v>
+        <v>1699000</v>
       </c>
       <c r="AL70" s="3">
         <v>1679700</v>
@@ -7609,7 +7776,7 @@
         <v>1679700</v>
       </c>
       <c r="AN70" s="3">
-        <v>1733900</v>
+        <v>1679700</v>
       </c>
       <c r="AO70" s="3">
         <v>1733900</v>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>1733900</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>1733900</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9214100</v>
+      </c>
+      <c r="E72" s="3">
         <v>9154200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9428100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9332400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9348500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8839900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8907900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9702800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8964300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9057500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9205500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8771800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8746400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8425700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8751600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>11390500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>11501600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>11038900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10892900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10392600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9645600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9584700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9508600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9097700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8970400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8820800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>8824300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9049100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9166500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>8793700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>8575200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>8096800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8286700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>7994600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>7669100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>7765800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>7402700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>7415700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>7190600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>6811100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17127000</v>
+      </c>
+      <c r="E76" s="3">
         <v>16846200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16766600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16843400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16778800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16506800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16550800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17476600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16344600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16468300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16507300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15805600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15718900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15549000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15132900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19299000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18872300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18439200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19082800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18524400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17359400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17595700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18245000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18096500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>18150300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>18044400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17333600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>18173600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>16992000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>16570400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>16982200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14953100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15777700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15467600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14931800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14914700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14928100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>15340000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>15133400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>14862900</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>725300</v>
+      </c>
+      <c r="E81" s="3">
         <v>347500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>541200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>808400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>538900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>659500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>178600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1012600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>486600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>618900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>582300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>657900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>513500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>610500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>925300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>80900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>687300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>483500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>798100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>754800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>650900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>703600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>575700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>575000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>407300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>307000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>560600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>564600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>471800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>479600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>441400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>412000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>531500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>503600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>154100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>608000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>427200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>423300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>559300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>566200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,52 +8961,53 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
         <v>182100</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
         <v>188500</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>178100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8886,8 +9084,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>81700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1558200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>875900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>847200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>586600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-265800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>425300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2398300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>852700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1836600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2576800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1404500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>218200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>672800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1373700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1465400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-342400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1480700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>655600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>196000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-760600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>897600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2264700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2398200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>65200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1309800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>160000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1507500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-944600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1433100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>812400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>303400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>323700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>483700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>468900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>983800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-474800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1057900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>491700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-33500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-21600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-24400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-34000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-31700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-50300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-21000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-32000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-40000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-23100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-31000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-33700</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-29000</v>
       </c>
       <c r="AB91" s="3">
         <v>-29000</v>
       </c>
       <c r="AC91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-35100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-14100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-23900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-38800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-21100</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AJ91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-35700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-29800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-24600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-64500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-105000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-38900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-55700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-125800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-55500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-70900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>11800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-182500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-102000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>48300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-180300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-92700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-70000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1913200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-37800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>197700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-131100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-57900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-610400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-103700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-430100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-73800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-76100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-98200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-175800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-28500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-101200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-41400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-51200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-16600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-104900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-49100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-111600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>13800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-77600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-116000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,86 +10471,89 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R96" s="3">
         <v>-318700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-300200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-320000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-285700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-305000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-250400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-245200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-254500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-263100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-259100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-267600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-267700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-266600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-270300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-262500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-245600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-240500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-223100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-231900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-222800</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-221000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-214300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-217300</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-213600</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-212800</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-206700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2157800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-87500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-633500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1142400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-708200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1216900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-214800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-683100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-483900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1054900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-570900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-195100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-563100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-155200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>931900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-257400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>889900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1030400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>350000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-416700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>360600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2221700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>446500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-352500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-704000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-135100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-551900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-462700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-475700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-426600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-299600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-719700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-14900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-337100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-277600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-901100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-574600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>456300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-183300</v>
+      </c>
+      <c r="E101" s="3">
         <v>13200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>232800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-33300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>34300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>99000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-218800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>167800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-55900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-24400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-34000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>243300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>60600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-51300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-33900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>243400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>57600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-46500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-9600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>71900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-40500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-47300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-183400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-37600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-127900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>280300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-52200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>29000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-64200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-59300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>153700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-48000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>57200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>26800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-77400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-59500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-23800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>50700</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>113400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-636900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>617000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>898100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-269100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1450600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-175800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1092600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>601300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2408900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1691600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>415500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-360200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-385100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1391900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>541700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-684100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-402800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-434100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>447700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1835100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>971100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-270600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2672800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-270800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>408500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-132600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>847700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1495000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1010000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>296500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-18800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-355300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>390700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>5200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>535100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1385900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>456300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>863500</v>
       </c>
     </row>
